--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -821,6 +821,200 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133869701</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83316</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>595525</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6988230</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133869700</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79429</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>967</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595526</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6988232</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -827,7 +827,7 @@
         <v>133869701</v>
       </c>
       <c r="B3" t="n">
-        <v>83316</v>
+        <v>83318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -827,7 +827,7 @@
         <v>133869701</v>
       </c>
       <c r="B3" t="n">
-        <v>83318</v>
+        <v>83319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -827,7 +827,7 @@
         <v>133869701</v>
       </c>
       <c r="B3" t="n">
-        <v>83319</v>
+        <v>83333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>133869700</v>
       </c>
       <c r="B4" t="n">
-        <v>79429</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -827,7 +827,7 @@
         <v>133869701</v>
       </c>
       <c r="B3" t="n">
-        <v>83333</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>133869700</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -827,7 +827,7 @@
         <v>133869701</v>
       </c>
       <c r="B3" t="n">
-        <v>83343</v>
+        <v>83344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>133869700</v>
       </c>
       <c r="B4" t="n">
-        <v>79453</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -827,7 +827,7 @@
         <v>133869701</v>
       </c>
       <c r="B3" t="n">
-        <v>83344</v>
+        <v>83351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>133869700</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17223343</v>
+        <v>17223342</v>
       </c>
       <c r="B2" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>595551.197956826</v>
+        <v>595535</v>
       </c>
       <c r="R2" t="n">
-        <v>6988227.935224396</v>
+        <v>6988175</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2012-09-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +787,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # Standing dead tree/snags # 0 # Pinus sylvestris</t>
+          <t>1 substratenheter # Standing dead tree/snags # talltorraka # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -824,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133869701</v>
+        <v>17223343</v>
       </c>
       <c r="B3" t="n">
-        <v>83351</v>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,34 +820,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Galantmyran, Jmt</t>
+          <t>Söråsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595525</v>
+        <v>595551</v>
       </c>
       <c r="R3" t="n">
-        <v>6988230</v>
+        <v>6988228</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,12 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,26 +890,63 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandmyr med tall</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Landskap med myrmarker</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Standing dead tree/snags # 0 # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Teo Jernkvist</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Teo Jernkvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133869700</v>
+        <v>17223345</v>
       </c>
       <c r="B4" t="n">
-        <v>79461</v>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,14 +974,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galantmyran, Jmt</t>
+          <t>Söråsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595526</v>
+        <v>595456</v>
       </c>
       <c r="R4" t="n">
-        <v>6988232</v>
+        <v>6988361</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,12 +1008,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2012-09-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,19 +1024,250 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandmyr med tall</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Landskap med myrmarker</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Standing dead tree/snags # 0 # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Caroline Westerlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133869700</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79468</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>967</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Varglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Letharia vulpina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>595526</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6988232</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Teo Jernkvist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Teo Jernkvist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133869701</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>595525</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6988230</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Teo Jernkvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51916-2021 artfynd.xlsx
+++ b/artfynd/A 51916-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17223342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -940,6 +950,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17223343</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1074,6 +1089,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17223345</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1171,6 +1191,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133869700</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,8 +1293,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133869701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>